--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_KN.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_KN.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R373f9e810b154f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Ra798847c02274d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R2f790c72a21d4704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rfaed465a10174d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rb535a9ccaaf04dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R3f3a4a6ed9e94acc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Ra1fc33569ff24dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R21bd135b6cc54d14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R4a836fe300a14b2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rb0ca5b1a11bd409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R3d67b83bb39140b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R1fe925e8ef7a4469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Re5e54ff0349c4efa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rf478de9e13eb492d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rf6ce42018e394785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R859f8d7cc9f541e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R9bff2da5ad904ab4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rc729db245df14bb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R80f46bd949824fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R7a1559bce3c14bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R259d443981314235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R22544db59abb4aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rcb3a99daa2ed4989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R7c2d8d53e5354f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R5426698fc3064099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rb46bd2b443124743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rdbfdbed3be494917"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R386671165f2844ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rac46790f0e7b4c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R2edc43bca54c4d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Ra30b16ebeec14739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R3de6b80ac5024bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R4fa01f1b61614709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R6236795892464ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rd45029c9fcc84a12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R98c588568e564781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rdfe1845524874528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R8936394113b34fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R4134b2f8ee04467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rae5cf39b66384c23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Ra11a7345758b422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R4fd09f1a20534597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R9bb86c6959b34a2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2786,6 +2787,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>菫(すみれ)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>鳥の国・ソナン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_KN.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_KN.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R22544db59abb4aeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rcb3a99daa2ed4989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R7c2d8d53e5354f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R5426698fc3064099"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rb46bd2b443124743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rdbfdbed3be494917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R386671165f2844ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rac46790f0e7b4c76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R2edc43bca54c4d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Ra30b16ebeec14739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R3de6b80ac5024bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R4fa01f1b61614709"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R6236795892464ad2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rd45029c9fcc84a12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R98c588568e564781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rdfe1845524874528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R8936394113b34fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R4134b2f8ee04467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rae5cf39b66384c23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Ra11a7345758b422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R4fd09f1a20534597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R9bb86c6959b34a2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rb8b96bfa077d418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R42fbdfdd9ee04074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Ra11b10a2451948b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R944a77a0827b452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R296c8730eb0b4564"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Ra15ed4c69ca7424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R27986f9ecedd4c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Re62bc124bfc24b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R66c96304182943c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R4992b52aa9ef4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R0399a212850148a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R3b07552973c940f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R7db019e24f2143a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rf3324afa1f894512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R1de681acfeac40d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R3153d879cf664dcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Re5525dba56a24b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R24833bac6f1545bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R447947ecac29451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Redb1de5656b84bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R747fec2390ea4ab3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R96efff7f820642ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -573,7 +573,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -618,11 +618,11 @@
         <x:v>PvE PvP ｜系列 無欠 無欠 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 無欠 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적이 알아차리지 못할 정도의 속도로 접근하여 급소를 찌른다."</x:v>
       </x:c>
@@ -633,11 +633,11 @@
         <x:v>「敵が気付かない速さで接近し、急所を刺す」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「敵が気付かない速さで接近し、急所を刺す」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>敵が気づかないほどの速度で接近し、急所を突く。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -648,11 +648,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 5초</x:v>
       </x:c>
@@ -663,82 +663,100 @@
         <x:v>・再使用待機時間: 5秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 5秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1833.85%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ916.93%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・무기 선택 : 소검 적용 시</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・When Weapon Selection: Shortsword is applied</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・武器選択：小剣適用時</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
         <x:v>・武器選択：小剣適用時</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>　・분신을 소환하여 동일한 기술 피해 로 추가 타격</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>　・Summons a clone for additional hit with same skill damage</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>　・同じ技術被害量で追加ヒットのクローンを召喚します</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>　・同じ技術被害量で追加ヒットのクローンを召喚します</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" t="str">
+        <x:v>　分身を召喚して同一のスキルダメージで追加打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>　・인 1 회 추가 적용</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>　・Forms 1 additional Seal</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>　・追加のシールを 1 つ形成します</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>　・追加のシールを 1 つ形成します</x:v>
+      <x:c r="E13" t="str">
+        <x:v>　印1回追加適用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -758,7 +776,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -786,7 +804,7 @@
         <x:v>熙演舞</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>熙演舞</x:v>
+        <x:v>廻天連舞</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -803,11 +821,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"사하륜을 양손으로 잡은 뒤 원심력을 이용하여 주위의 적에게 큰 피해를 입힌다."</x:v>
       </x:c>
@@ -818,11 +836,11 @@
         <x:v>「月輪を両手で握り、遠心力を利用して周囲の敵に大ダメージを与える。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「月輪を両手で握り、遠心力を利用して周囲の敵に大ダメージを与える。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>月輪刀を両手で掴んで遠心力を利用して周囲の敵に大ダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -833,11 +851,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 6초</x:v>
       </x:c>
@@ -848,52 +866,70 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1493.54%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ746.77%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 6 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 6 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大6ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大6ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大6打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -913,7 +949,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -941,7 +977,7 @@
         <x:v>手裏剣投げ</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>手裏剣投げ</x:v>
+        <x:v>苦無投擲</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -958,11 +994,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"빠르게 움직이며 수리검을 적에게 던져 적을 공격한다."</x:v>
       </x:c>
@@ -973,11 +1009,11 @@
         <x:v>素早く動き、手裏剣を投げて敵を攻撃する。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>素早く動き、手裏剣を投げて敵を攻撃する。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>素早く動きながら苦無を敵に投げて攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・소모 정신력 : 25</x:v>
       </x:c>
@@ -988,37 +1024,55 @@
         <x:v>・消費精神力：25</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・消費精神力：25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
-      <x:c r="B6" s="6" t="str">
+        <x:v>消費MP：25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6" t="str">
+        <x:v>・打撃ダメージ968.29%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・PVP打撃ダメージ484.15%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8"/>
+      <x:c r="B8" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
+      <x:c r="C8" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
+      <x:c r="D8" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E6" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+      <x:c r="E8" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9"/>
+      <x:c r="B9" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
+      <x:c r="E9" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1038,7 +1092,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1066,7 +1120,7 @@
         <x:v>神人分撃</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>神人分撃</x:v>
+        <x:v>月下撃攘</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1083,11 +1137,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"모든 분노를 사하륜에 담아 전방의 적을 높게 올려베고, 강하게 앞으로 쳐내며 큰 피해를 입힌다."</x:v>
       </x:c>
@@ -1098,11 +1152,11 @@
         <x:v>「三日月の刃に怒りを込めて、敵を前方へ上空へと切り裂き、強力に叩きつけて大ダメージを与える。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「三日月の刃に怒りを込めて、敵を前方へ上空へと切り裂き、強力に叩きつけて大ダメージを与える。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>すべての怒りを月輪刀に込めて前方の敵を斬り上げた後、月輪刀を前方に強く突き出して大ダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1113,11 +1167,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 8초</x:v>
       </x:c>
@@ -1128,52 +1182,70 @@
         <x:v>・再使用待機時間: 8秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 8秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：8秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1086.44%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ543.22%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 3 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 3 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大3ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大3ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大3打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Knockback on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時ノックバック</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックバック</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックバック</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1193,7 +1265,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1221,7 +1293,7 @@
         <x:v>他界落下</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>他界落下</x:v>
+        <x:v>飯綱落とし</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1238,11 +1310,11 @@
         <x:v>PvE PvP ｜系列 鮮明 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 鮮明 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적을 잡아 공중으로 도약한 후 바닥에 강하게 내려 꽃는다."</x:v>
       </x:c>
@@ -1253,11 +1325,11 @@
         <x:v>「敵を掴んで空中に飛び上がり、地面に叩きつける。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「敵を掴んで空中に飛び上がり、地面に叩きつける。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>敵を掴み空中へジャンプした後、地面に強く打ち下ろす。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1268,11 +1340,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 19초</x:v>
       </x:c>
@@ -1283,97 +1355,115 @@
         <x:v>・再使用待機時間: 19秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 19秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：19秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ753.83%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ376.92%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・잡기 시도 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・During grab attempt: Super Armor , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・掴みの試み中: スーパーアーマー、つかみ不可</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・掴みの試み中: スーパーアーマー、つかみ不可</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・キャッチ試行中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・점프 중 무적</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・While jumping: Invincible</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ジャンプ中：無敵</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ジャンプ中：無敵</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・ジャンプ中、無敵</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・착지 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・While landing: Super Armor</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・着陸時：スーパーアーマー</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・着陸時：スーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・着地中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・잡기 성공 시 바운드</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Bound on hit</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・ヒット時にバウンド</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・ヒット時にバウンド</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" t="str">
+        <x:v>・キャッチ成功時、バウンド</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・범위 내 타격 대상 동일 효과 적용</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・Same effect applied to hit targets within range</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・範囲内のターゲットにヒットした場合も同じ効果が適用されます</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・範囲内のターゲットにヒットした場合も同じ効果が適用されます</x:v>
+      <x:c r="E14" t="str">
+        <x:v>・範囲内の打撃対象に同一効果適用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1393,7 +1483,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1421,7 +1511,7 @@
         <x:v>忍術：隠れ身</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>忍術：隠れ身</x:v>
+        <x:v>忍術：潜伏</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1438,11 +1528,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적에게서 몸을 숨기는 술법을 사용한다."</x:v>
       </x:c>
@@ -1453,11 +1543,11 @@
         <x:v>敵から身を隠す術を使う。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>敵から身を隠す術を使う。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>敵から身を隠す忍術を使用する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1468,11 +1558,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 15초</x:v>
       </x:c>
@@ -1483,11 +1573,11 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
       <x:c r="B7" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
@@ -1498,11 +1588,11 @@
         <x:v>・即時発動技術</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
       <x:c r="B8" s="6" t="str">
         <x:v>・은신 시전 중 슈퍼 아머</x:v>
       </x:c>
@@ -1513,11 +1603,11 @@
         <x:v>・詠唱中のスーパーアーマー</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>・詠唱中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
+        <x:v>・潜伏準備中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
       <x:c r="B9" s="6" t="str">
         <x:v>・은신 후 0.5초 간 슈퍼 아머</x:v>
       </x:c>
@@ -1528,11 +1618,11 @@
         <x:v>・ステルス後0.5秒間のスーパーアーマー</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>・ステルス後0.5秒間のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
+        <x:v>・潜伏後、0.5秒間スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
       <x:c r="B10" s="6" t="str">
         <x:v>・은신 지속 시간 6초</x:v>
       </x:c>
@@ -1543,7 +1633,7 @@
         <x:v>・ステルス持続時間: 6秒</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>・ステルス持続時間: 6秒</x:v>
+        <x:v>・潜伏持続時間6秒</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1563,7 +1653,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1591,7 +1681,7 @@
         <x:v>冷静な精神</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>冷静な精神</x:v>
+        <x:v>精神統一</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1607,12 +1697,10 @@
       <x:c r="D3" s="6" t="str">
         <x:v>PvE PvP</x:v>
       </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+      <x:c r="E3" s="6"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"인술을 맺어 냉정하게 정신을 가다듬는다."</x:v>
       </x:c>
@@ -1623,11 +1711,11 @@
         <x:v>「忍術の印を結び、心を静かに集中させる。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「忍術の印を結び、心を静かに集中させる。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>忍術で精神を整え冷静さを保ち、自分を強化する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1638,11 +1726,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 120초</x:v>
       </x:c>
@@ -1653,11 +1741,11 @@
         <x:v>・再使用待機時間: 120秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 120秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
+        <x:v>再使用待機時間：93秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
       <x:c r="B7" s="6" t="str">
         <x:v>・10초 간 2초 마다 생명력 회복 115</x:v>
       </x:c>
@@ -1668,11 +1756,11 @@
         <x:v>・10秒間、2秒ごとに生命力回復115</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>・10秒間、2秒ごとに生命力回復115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
+        <x:v>・10秒間、2秒ごとにHP250回復</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
       <x:c r="B8" s="6" t="str">
         <x:v>・30초 간 공격력 +43</x:v>
       </x:c>
@@ -1683,11 +1771,11 @@
         <x:v>・30秒間AP +43</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>・30秒間AP +43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
+        <x:v>・30秒間、攻撃力+70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
       <x:c r="B9" s="6" t="str">
         <x:v>・30초 간 방어력 +43</x:v>
       </x:c>
@@ -1698,11 +1786,11 @@
         <x:v>・30秒間DP+43</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>・30秒間DP+43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
+        <x:v>・30秒間、防御力+70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
       <x:c r="B10" s="6" t="str">
         <x:v>・30초 간 치명타 피해량 +50%</x:v>
       </x:c>
@@ -1713,11 +1801,11 @@
         <x:v>・30秒間致命打被害量+50%</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>・30秒間致命打被害量+50%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
+        <x:v>・30秒間、クリティカルダメージ量+50%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
       <x:c r="B11" s="6" t="str">
         <x:v>・30초 간 흑정령 기술 피해량 +20%</x:v>
       </x:c>
@@ -1728,11 +1816,11 @@
         <x:v>・闇の精霊の怒り技術被害量+20% (30秒間)</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>・闇の精霊の怒り技術被害量+20% (30秒間)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
+        <x:v>・30秒間、闇の精霊スキルダメージ量+20%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
       <x:c r="B12" s="6" t="str">
         <x:v>・기술 사용 시 30초 간 회피 기술 재사용 시간 2초 감소</x:v>
       </x:c>
@@ -1743,7 +1831,7 @@
         <x:v>・技術使用時、30秒間回避再使用待機時間が2秒減少する</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>・技術使用時、30秒間回避再使用待機時間が2秒減少する</x:v>
+        <x:v>・スキル使用時30秒間、回避スキル再使用待機時間2秒減少</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1763,7 +1851,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1791,7 +1879,7 @@
         <x:v>一閃</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>一閃</x:v>
+        <x:v>廻閃</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1808,11 +1896,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적이 알아차리지 못할 정도의 속도로 적을 베어 내며 동시에 큰 피해를 준다."</x:v>
       </x:c>
@@ -1823,11 +1911,11 @@
         <x:v>「敵に気付かれない速さで斬り込み、大ダメージを与える。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「敵に気付かれない速さで斬り込み、大ダメージを与える。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>敵が気づかないほどの速度で敵を斬りつけ、同時に大きなダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1838,11 +1926,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 16초</x:v>
       </x:c>
@@ -1853,67 +1941,85 @@
         <x:v>・再使用待機時間: 16秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 16秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：16秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2131%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1065.5%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・은신 중 슈퍼 아머 , 피해 감소 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・While in stealth: Super Armor , Damage Reduction , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ステルス中: スーパーアーマー 、 被害減少 、 つかみ不可</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ステルス中: スーパーアーマー 、 被害減少 、 つかみ不可</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・潜伏中、スーパーアーマー、ダメージ減少、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1933,7 +2039,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1978,11 +2084,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"상대의 공격을 받아내며 순간적으로 반격해 피해를 준다."</x:v>
       </x:c>
@@ -1993,11 +2099,11 @@
         <x:v>「相手の攻撃を耐えながら瞬時に反撃する」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「相手の攻撃を耐えながら瞬時に反撃する」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>相手の攻撃を受け止めながら瞬時に反撃することで、ダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2008,11 +2114,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 15초</x:v>
       </x:c>
@@ -2023,52 +2129,70 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2938%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1469%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Forward Guard during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術中前衛ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Knockback on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時ノックバック</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックバック</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックバック</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2088,7 +2212,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2116,7 +2240,7 @@
         <x:v>鬼の挨拶</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>鬼の挨拶</x:v>
+        <x:v>影昇り</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2133,11 +2257,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"순간적으로 적 앞에 나타나 적을 공중에 띄워 올리며 피해를 준다."</x:v>
       </x:c>
@@ -2148,11 +2272,11 @@
         <x:v>瞬間的に敵の目の前に現れ、敵を空中に吹き飛ばし、ダメージを与えます。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>瞬間的に敵の目の前に現れ、敵を空中に吹き飛ばし、ダメージを与えます。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>瞬時に敵の前に現れ、敵を飛ばしてダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2163,11 +2287,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 15초</x:v>
       </x:c>
@@ -2178,37 +2302,55 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ3467%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1733.5%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9"/>
+      <x:c r="B9" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
+      <x:c r="E10" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2519,7 +2661,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2564,11 +2706,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"전방에 회전하는 사하륜을 날려 주변의 적에게 지속적인 피해를 입힌다."</x:v>
       </x:c>
@@ -2579,11 +2721,11 @@
         <x:v>「回転する月輪を前方に投げ、周囲の敵に継続的なダメージを与える。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「回転する月輪を前方に投げ、周囲の敵に継続的なダメージを与える。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>前方に回転する月輪刀を投げ、周辺の敵に継続的なダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2594,11 +2736,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 16초</x:v>
       </x:c>
@@ -2609,52 +2751,106 @@
         <x:v>・再使用待機時間: 16秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 16秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：16秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2820%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1410%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor , Grab Immunity during skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・スーパーアーマー、技術中の獲得免疫</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・スーパーアーマー、技術中の獲得免疫</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 지점에 사하륜의 영역 생성</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Creates a Crescent Blade Zone at the hit point</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒットポイントに月輪ゾーンを生成</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒットポイントに月輪ゾーンを生成</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃地点に月輪刀の領域生成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12" t="str">
+        <x:v>・月輪刀の領域</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13" t="str">
+        <x:v>　打撃ダメージ1410%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>　PVP打撃ダメージ705%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　最大6打撃</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2944,7 +3140,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2972,7 +3168,7 @@
         <x:v>黒い月光</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>黒い月光</x:v>
+        <x:v>黒い片時雨</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2989,11 +3185,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"자신의 몸을 숨긴 후 적에게 수 많은 표창과 수리검을 떨어뜨려 큰 피해를 입힌다."</x:v>
       </x:c>
@@ -3004,11 +3200,11 @@
         <x:v>「身を隠し、敵に無数の手裏剣やクナイを投下して大ダメージを与える。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「身を隠し、敵に無数の手裏剣やクナイを投下して大ダメージを与える。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>身を隠した後、敵に数多くの手裏剣と苦無を落とし大ダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3019,11 +3215,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 8초</x:v>
       </x:c>
@@ -3034,67 +3230,85 @@
         <x:v>・再使用待機時間: 8秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 8秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：8秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1258.53%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ629.26%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 5 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 5 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大5ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大5ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大5打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・점프 중 잡기 불가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Grab Immunity while jumping</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ジャンプ中に免疫を獲得する</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ジャンプ中に免疫を獲得する</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・ジャンプ中、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・타격 성공 시 바운드</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Bound on hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・ヒット時にバウンド</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒット時にバウンド</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・打撃成功時、バウンド</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3114,7 +3328,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3142,7 +3356,7 @@
         <x:v>影踏み</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>影踏み</x:v>
+        <x:v>影縫い</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3159,11 +3373,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"전방으로 빠르게 이동하여 사하륜과 함께 상대를 밟아 피해를 준다."</x:v>
       </x:c>
@@ -3174,11 +3388,11 @@
         <x:v>「素早く前進して月輪で敵を踏みつける。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「素早く前進して月輪で敵を踏みつける。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>前方に素早く移動した後、月輪刀の上から相手を踏みつけてダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3189,11 +3403,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 9초</x:v>
       </x:c>
@@ -3204,82 +3418,118 @@
         <x:v>・再使用待機時間: 9秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 9秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：9秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1331.73%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ665.86%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Instant Activation Skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・即時発動技術</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・무기 선택 : 소검 적용 시 기술 피해량의 100% 추가 피해 적용</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Applies 100% additional skill damage when Weapon Selection: Shortsword is applied</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・武器選択: 小剣が適用されると、100% の追加技術 ダメージを適用します</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・武器選択: 小剣が適用されると、100% の追加技術 ダメージを適用します</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" t="str">
+        <x:v>・武器選択：小剣適用時</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13" t="str">
+        <x:v>　スキルダメージ量の100%追加ダメージ適用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・무기 선택 : 사하륜 적용 시 공격 위치에 달빛 영역 생성</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・Creates a Moonlight Zone at the attack position when Weapon Selection: Crescent Blade is applied</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・武器選択：月輪適用時、攻撃位置に月光ゾーンを生成</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・武器選択：月輪適用時、攻撃位置に月光ゾーンを生成</x:v>
+      <x:c r="E14" t="str">
+        <x:v>・武器選択：月輪刀適用時</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　攻撃位置に月光の領域生成</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3299,7 +3549,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3327,7 +3577,7 @@
         <x:v>腱切り</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>腱切り</x:v>
+        <x:v>腱断ち</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3344,11 +3594,11 @@
         <x:v>PvE PvP ｜系列 燦爛 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 燦爛 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"강력한 살의를 담아 빠르게 움직이며 상대를 베어낸다."</x:v>
       </x:c>
@@ -3359,11 +3609,11 @@
         <x:v>「強力な殺意を持って素早く動き、敵を斬る。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「強力な殺意を持って素早く動き、敵を斬る。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>強力な殺意を込めて素早く動きながら相手を斬る。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3374,11 +3624,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 6초</x:v>
       </x:c>
@@ -3389,82 +3639,100 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ809.05%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ404.52%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 7 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 7 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大7ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大7ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大7打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Instant Activation Skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・即時発動技術</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・마지막 타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Successfull last hit applies Knockback</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・最後のヒットに成功するとノックバックが適用されます</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・最後のヒットに成功するとノックバックが適用されます</x:v>
+      <x:c r="E13" t="str">
+        <x:v>・最後の打撃成功時、ノックバック</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3484,7 +3752,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3512,7 +3780,7 @@
         <x:v>驚嘆錘</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>驚嘆錘</x:v>
+        <x:v>月輪ノ矢</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3529,11 +3797,11 @@
         <x:v>PvE PvP ｜系列 鮮明 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 鮮明 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"힘이 실린 사하륜의 기운을 전방에 내뿜는다."</x:v>
       </x:c>
@@ -3544,11 +3812,11 @@
         <x:v>「月輪の強力なエネルギーを前方に吐き出す。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「月輪の強力なエネルギーを前方に吐き出す。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>力が込められた月輪刀のオーラを前方に放つ。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3559,11 +3827,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 6초</x:v>
       </x:c>
@@ -3574,37 +3842,55 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1579.58%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ789.79%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9"/>
+      <x:c r="B9" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" t="str">
         <x:v>・Forward Guard during skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" t="str">
         <x:v>・技術中前衛ガード</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術中前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
+      <x:c r="E10" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3624,7 +3910,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3652,7 +3938,7 @@
         <x:v>殺舞</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>殺舞</x:v>
+        <x:v>殺迅</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3669,11 +3955,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"수리검을 날린 대상을 추적하고 순식간에 추적한 대상에게 접근하여 공격한다."</x:v>
       </x:c>
@@ -3684,11 +3970,11 @@
         <x:v>投げた手裏剣の標的を追跡し、素早く近づいて攻撃する。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>投げた手裏剣の標的を追跡し、素早く近づいて攻撃する。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>苦無を投げた対象を追跡し、瞬時に接近して攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3699,11 +3985,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 7초</x:v>
       </x:c>
@@ -3714,67 +4000,85 @@
         <x:v>・再使用待機時間: 7秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 7秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1232.84%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ616.42%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor during skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術中のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術中のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・마지막 타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Stiffness on last hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・ラストヒット時の硬さ</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ラストヒット時の硬さ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・最後の打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・기술 재사용 시 추가 타격</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Additional hit when reusing skill</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・技術再使用時追加ヒット</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・技術再使用時追加ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・スキル再使用時、追加打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・기술 버튼 유지 시 대상에게 순간 이동 후 추가 타격</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・When holding the skill button, Teleport to the target and additional hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・技術ボタンを押し続けるとターゲットにテレポートして追加ヒットします</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・技術ボタンを押し続けるとターゲットにテレポートして追加ヒットします</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・スキルボタン長押しで瞬間移動した後、対象に追加打撃</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3794,7 +4098,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3839,11 +4143,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"쿠레나이의 손을 벗어난 사하륜은 인정사정 없이 적진을 파헤친다."</x:v>
       </x:c>
@@ -3854,11 +4158,11 @@
         <x:v>「紅の手から繰り出される三日月の刃は、容赦なく敵陣を切り裂く。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「紅の手から繰り出される三日月の刃は、容赦なく敵陣を切り裂く。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>クノーの手から離れた月輪刀は、容赦なく敵陣を突き抜く。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3869,11 +4173,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기 시간 : 7초</x:v>
       </x:c>
@@ -3884,52 +4188,70 @@
         <x:v>・再使用待機時間: 7秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 7秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：7秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ934.91%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ467.45%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 4 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 4 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大4ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大4ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大4打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Forward Guard during skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術中前衛ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術中前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
